--- a/results/pr_AstroSync/exp/14BE/cv_scores/fair_cv_summary.xlsx
+++ b/results/pr_AstroSync/exp/14BE/cv_scores/fair_cv_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -858,7 +858,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -886,10 +886,10 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.007623580693716964</v>
+        <v>0.007445547943798488</v>
       </c>
       <c r="O8" t="n">
-        <v>0.02172940912769573</v>
+        <v>0.02135134910370442</v>
       </c>
     </row>
     <row r="9">
@@ -910,43 +910,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F9" t="n">
         <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05773502691896256</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.9696969696969697</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.9444444444444445</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01126013329769626</v>
+        <v>0.007623580693716964</v>
       </c>
       <c r="O9" t="n">
-        <v>0.02993582564252469</v>
+        <v>0.02172940912769573</v>
       </c>
     </row>
     <row r="10">
@@ -967,12 +967,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -1000,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.01527866168266367</v>
+        <v>0.01126013329769626</v>
       </c>
       <c r="O10" t="n">
-        <v>0.03768866605223269</v>
+        <v>0.02993582564252469</v>
       </c>
     </row>
     <row r="11">
@@ -1024,12 +1024,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -1057,10 +1057,10 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01909742591517313</v>
+        <v>0.01523055336498365</v>
       </c>
       <c r="O11" t="n">
-        <v>0.04715612502010397</v>
+        <v>0.03760363551948197</v>
       </c>
     </row>
     <row r="12">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -1114,10 +1114,10 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.03053298082850973</v>
+        <v>0.01527866168266367</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1049536009412178</v>
+        <v>0.03768866605223269</v>
       </c>
     </row>
     <row r="13">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -1171,10 +1171,10 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.03132604409497568</v>
+        <v>0.01856938794485</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1163066866885131</v>
+        <v>0.045730478340559</v>
       </c>
     </row>
     <row r="14">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1228,10 +1228,10 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03297658424793459</v>
+        <v>0.01909742591517313</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1742621110574057</v>
+        <v>0.04715612502010397</v>
       </c>
     </row>
     <row r="15">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -1285,10 +1285,10 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03330132981900364</v>
+        <v>0.02909854719160476</v>
       </c>
       <c r="O15" t="n">
-        <v>0.25340338054649</v>
+        <v>0.09077596818052924</v>
       </c>
     </row>
     <row r="16">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -1342,10 +1342,10 @@
         <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>0.03333058034044743</v>
+        <v>0.03053298082850973</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3089022818909907</v>
+        <v>0.1049536009412178</v>
       </c>
     </row>
     <row r="17">
@@ -1366,12 +1366,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1396,13 +1396,13 @@
         <v>0.9444444444444445</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9866666666666667</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.03333332677972797</v>
+        <v>0.03116281592191332</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5273404482569081</v>
+        <v>0.1139348845967737</v>
       </c>
     </row>
     <row r="18">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1456,10 +1456,10 @@
         <v>1</v>
       </c>
       <c r="N18" t="n">
-        <v>0.03333388472677377</v>
+        <v>0.03132604409497568</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6197409315858513</v>
+        <v>0.1163066866885131</v>
       </c>
     </row>
     <row r="19">
@@ -1480,12 +1480,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1510,13 +1510,13 @@
         <v>0.9444444444444445</v>
       </c>
       <c r="M19" t="n">
-        <v>0.9866666666666667</v>
+        <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>0.03333752818096582</v>
+        <v>0.03297658424793459</v>
       </c>
       <c r="O19" t="n">
-        <v>1.006861210651082</v>
+        <v>0.1742621110574057</v>
       </c>
     </row>
     <row r="20">
@@ -1537,12 +1537,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1567,13 +1567,13 @@
         <v>0.9444444444444445</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9866666666666667</v>
+        <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.03342790841469017</v>
+        <v>0.03310629103292944</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4686302334680674</v>
+        <v>0.1893541520511601</v>
       </c>
     </row>
     <row r="21">
@@ -1599,26 +1599,26 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>3</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05773502691896258</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I21" t="n">
-        <v>0.9333333333333332</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J21" t="n">
-        <v>0.9326599326599326</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0.9444444444444445</v>
@@ -1627,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.06666585022595442</v>
+        <v>0.03330132981900364</v>
       </c>
       <c r="O21" t="n">
-        <v>0.82411359226734</v>
+        <v>0.25340338054649</v>
       </c>
     </row>
     <row r="22">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1656,38 +1656,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M22" t="n">
         <v>1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.836867571883356e-34</v>
+        <v>0.03330336226835757</v>
       </c>
       <c r="O22" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.2497539731859114</v>
       </c>
     </row>
     <row r="23">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1708,43 +1708,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J23" t="n">
-        <v>1</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M23" t="n">
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.099271404210207e-34</v>
+        <v>0.03333058034044743</v>
       </c>
       <c r="O23" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0.3089022818909907</v>
       </c>
     </row>
     <row r="24">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1765,43 +1765,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[9, 13]</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K24" t="n">
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M24" t="n">
-        <v>1</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N24" t="n">
-        <v>8.254162977703491e-26</v>
+        <v>0.03333332677972797</v>
       </c>
       <c r="O24" t="n">
-        <v>8.093525849521517e-14</v>
+        <v>0.5273404482569081</v>
       </c>
     </row>
     <row r="25">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1834,31 +1834,31 @@
         <v>3</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K25" t="n">
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M25" t="n">
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.730006368373841e-24</v>
+        <v>0.03333388472677377</v>
       </c>
       <c r="O25" t="n">
-        <v>4.233835504426685e-13</v>
+        <v>0.6197409315858513</v>
       </c>
     </row>
     <row r="26">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1884,38 +1884,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>3</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J26" t="n">
-        <v>1</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M26" t="n">
-        <v>1</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N26" t="n">
-        <v>1.789794523625118e-23</v>
+        <v>0.03333752818096582</v>
       </c>
       <c r="O26" t="n">
-        <v>7.729705764437215e-13</v>
+        <v>1.006861210651082</v>
       </c>
     </row>
     <row r="27">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1)</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>3</v>
       </c>
       <c r="G27" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J27" t="n">
-        <v>1</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K27" t="n">
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M27" t="n">
-        <v>1</v>
+        <v>0.9866666666666667</v>
       </c>
       <c r="N27" t="n">
-        <v>1.868610928512374e-23</v>
+        <v>0.03342790841469017</v>
       </c>
       <c r="O27" t="n">
-        <v>7.895091987676154e-13</v>
+        <v>0.4686302334680674</v>
       </c>
     </row>
     <row r="28">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1993,43 +1993,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>3</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.05773502691896256</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="J28" t="n">
-        <v>1</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M28" t="n">
         <v>1</v>
       </c>
       <c r="N28" t="n">
-        <v>4.619280397332615e-20</v>
+        <v>0.03348037253207976</v>
       </c>
       <c r="O28" t="n">
-        <v>4.815461735378691e-11</v>
+        <v>0.6872107248280687</v>
       </c>
     </row>
     <row r="29">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>qm_rec_calib.hdf</t>
+          <t>im_rec_calib.hdf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2050,43 +2050,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>3</v>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.05773502691896258</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="J29" t="n">
-        <v>1</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>0.9333333333333332</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0.9444444444444445</v>
       </c>
       <c r="M29" t="n">
         <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>3.136192762239447e-15</v>
+        <v>0.06666585022595442</v>
       </c>
       <c r="O29" t="n">
-        <v>1.094743141962334e-08</v>
+        <v>0.82411359226734</v>
       </c>
     </row>
     <row r="30">
@@ -2107,12 +2107,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -2140,10 +2140,10 @@
         <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>7.583973614259139e-15</v>
+        <v>2.836867571883356e-34</v>
       </c>
       <c r="O30" t="n">
-        <v>2.317235010783145e-08</v>
+        <v>2.220446049250313e-16</v>
       </c>
     </row>
     <row r="31">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, -2, -1)</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -2197,10 +2197,10 @@
         <v>1</v>
       </c>
       <c r="N31" t="n">
-        <v>9.188620503202899e-15</v>
+        <v>3.099271404210207e-34</v>
       </c>
       <c r="O31" t="n">
-        <v>2.509967686084177e-08</v>
+        <v>2.220446049250313e-16</v>
       </c>
     </row>
     <row r="32">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>(0, 1, -1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -2254,10 +2254,10 @@
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>1.163315866549829e-12</v>
+        <v>8.254162977703491e-26</v>
       </c>
       <c r="O32" t="n">
-        <v>1.972258984309494e-07</v>
+        <v>8.093525849521517e-14</v>
       </c>
     </row>
     <row r="33">
@@ -2283,7 +2283,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -2311,10 +2311,10 @@
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>3.079771540415258e-12</v>
+        <v>3.730006368373841e-24</v>
       </c>
       <c r="O33" t="n">
-        <v>4.455679983703113e-07</v>
+        <v>4.233835504426685e-13</v>
       </c>
     </row>
     <row r="34">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>[8, 15]</t>
+          <t>[10, 14]</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>(0, -1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -2368,10 +2368,10 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55701028362444e-12</v>
+        <v>1.451922581633607e-23</v>
       </c>
       <c r="O34" t="n">
-        <v>3.662444365996449e-07</v>
+        <v>8.388697144403665e-13</v>
       </c>
     </row>
     <row r="35">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>(0, 1, -2, -1)</t>
+          <t>(0, 1, -1)</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -2425,10 +2425,10 @@
         <v>1</v>
       </c>
       <c r="N35" t="n">
-        <v>6.929460153402813e-12</v>
+        <v>1.789794523625118e-23</v>
       </c>
       <c r="O35" t="n">
-        <v>4.818827533278856e-07</v>
+        <v>7.729705764437215e-13</v>
       </c>
     </row>
     <row r="36">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, -1)</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -2482,10 +2482,10 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.463764891725277e-10</v>
+        <v>1.868610928512374e-23</v>
       </c>
       <c r="O36" t="n">
-        <v>2.881859145782623e-06</v>
+        <v>7.895091987676154e-13</v>
       </c>
     </row>
     <row r="37">
@@ -2506,31 +2506,31 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>(0, -2, -1)</t>
+          <t>(0, 2, -1)</t>
         </is>
       </c>
       <c r="F37" t="n">
         <v>3</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0577350269189626</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9666666666666667</v>
+        <v>1</v>
       </c>
       <c r="J37" t="n">
-        <v>0.9629629629629629</v>
+        <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>0.9333333333333332</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -2539,10 +2539,10 @@
         <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>0.03586470682971387</v>
+        <v>3.781388490889041e-21</v>
       </c>
       <c r="O37" t="n">
-        <v>0.1108062791034568</v>
+        <v>1.122740049268191e-11</v>
       </c>
     </row>
     <row r="38">
@@ -2563,43 +2563,43 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>[9, 13]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, -2, -1)</t>
         </is>
       </c>
       <c r="F38" t="n">
         <v>3</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J38" t="n">
-        <v>0.914141414141414</v>
+        <v>1</v>
       </c>
       <c r="K38" t="n">
         <v>1</v>
       </c>
       <c r="L38" t="n">
-        <v>0.8492063492063492</v>
+        <v>1</v>
       </c>
       <c r="M38" t="n">
         <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0.08345506377257043</v>
+        <v>4.619280397332615e-20</v>
       </c>
       <c r="O38" t="n">
-        <v>0.4782719543970801</v>
+        <v>4.815461735378691e-11</v>
       </c>
     </row>
     <row r="39">
@@ -2620,43 +2620,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>[10, 14]</t>
+          <t>[8, 12]</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F39" t="n">
         <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>0.914141414141414</v>
+        <v>1</v>
       </c>
       <c r="K39" t="n">
         <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.8492063492063492</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
         <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.08560951598391459</v>
+        <v>1.128314132300033e-19</v>
       </c>
       <c r="O39" t="n">
-        <v>0.4111156974782124</v>
+        <v>6.132796498505259e-11</v>
       </c>
     </row>
     <row r="40">
@@ -2677,43 +2677,43 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>[8, 12]</t>
+          <t>[8, 15]</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>(0, 1)</t>
+          <t>(0, 1, 2, -1)</t>
         </is>
       </c>
       <c r="F40" t="n">
         <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>0.1732050807568878</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0.923076923076923</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
         <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0.875</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0.09891927091215021</v>
+        <v>2.619553249924953e-18</v>
       </c>
       <c r="O40" t="n">
-        <v>0.9639912318999727</v>
+        <v>3.900958125188557e-10</v>
       </c>
     </row>
     <row r="41">
@@ -2739,37 +2739,949 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
+          <t>(0, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.362513299900871e-16</v>
+      </c>
+      <c r="O41" t="n">
+        <v>3.006340072884302e-09</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>3</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>3.136192762239447e-15</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.094743141962334e-08</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>(0, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7.224371462744146e-15</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.55487472529603e-08</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>3</v>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>7.583973614259139e-15</v>
+      </c>
+      <c r="O44" t="n">
+        <v>2.317235010783145e-08</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>3</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>9.188620503202899e-15</v>
+      </c>
+      <c r="O45" t="n">
+        <v>2.509967686084177e-08</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>(0, 1, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4.669743535063053e-13</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.248345222827099e-07</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>(0, 1, -1)</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.163315866549829e-12</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.972258984309494e-07</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>3</v>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1</v>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.079771540415258e-12</v>
+      </c>
+      <c r="O48" t="n">
+        <v>4.455679983703113e-07</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>(0, -1)</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3</v>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.55701028362444e-12</v>
+      </c>
+      <c r="O49" t="n">
+        <v>3.662444365996449e-07</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>(0, 1, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" t="n">
+        <v>6.929460153402813e-12</v>
+      </c>
+      <c r="O50" t="n">
+        <v>4.818827533278856e-07</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>3</v>
+      </c>
+      <c r="G51" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.463764891725277e-10</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.881859145782623e-06</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>(0, 2, -1)</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>3</v>
+      </c>
+      <c r="G52" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>1</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" t="n">
+        <v>4.057328695633805e-10</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3.687517672291345e-06</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>(0, -2, -1)</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>3</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.0577350269189626</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.9629629629629629</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.9333333333333332</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.03586470682971387</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.1108062791034568</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>[9, 13]</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>(0, 1)</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>3</v>
-      </c>
-      <c r="G41" t="n">
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.914141414141414</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.08345506377257043</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.4782719543970801</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>[10, 14]</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.09999999999999998</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.914141414141414</v>
+      </c>
+      <c r="K55" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.8492063492063492</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.08560951598391459</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.4111156974782124</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>[8, 12]</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>3</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.1732050807568878</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.09891927091215021</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.9639912318999727</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14BE</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>qm_rec_calib.hdf</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>lda</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>[8, 15]</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>(0, 1)</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H41" t="n">
+      <c r="H57" t="n">
         <v>0.1527525231651947</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I57" t="n">
         <v>0.8666666666666667</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J57" t="n">
         <v>0.8927738927738927</v>
       </c>
-      <c r="K41" t="n">
-        <v>1</v>
-      </c>
-      <c r="L41" t="n">
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
         <v>0.8194444444444445</v>
       </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="n">
+      <c r="M57" t="n">
+        <v>1</v>
+      </c>
+      <c r="N57" t="n">
         <v>0.1277479800404862</v>
       </c>
-      <c r="O41" t="n">
+      <c r="O57" t="n">
         <v>0.6334394596247993</v>
       </c>
     </row>
